--- a/docs/d/46/inyear.xlsx
+++ b/docs/d/46/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 86 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 84 clubs short</t>
         </is>
       </c>
     </row>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12515,8 +12515,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -17605,7 +17605,7 @@
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>10</v>
@@ -17649,7 +17649,7 @@
         <v>0</v>
       </c>
       <c r="Q169" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R169" s="9" t="n">
         <v>0</v>
@@ -17675,8 +17675,8 @@
       <c r="Y169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z169" s="9" t="n">
-        <v>0</v>
+      <c r="Z169" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA169" s="10" t="n">
         <v>1</v>
@@ -18993,7 +18993,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -19356,7 +19356,7 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>

--- a/docs/d/46/inyear.xlsx
+++ b/docs/d/46/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,11 @@
       <c r="AB13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC13" s="4" t="inlineStr"/>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2252,7 +2256,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2353,7 +2361,11 @@
       <c r="AB16" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2660,7 +2672,11 @@
       <c r="AB19" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC19" s="4" t="inlineStr"/>
+      <c r="AC19" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2761,7 +2777,11 @@
       <c r="AB20" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3064,7 +3084,11 @@
       <c r="AB23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -5193,7 +5217,11 @@
       <c r="AB44" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC44" s="4" t="inlineStr"/>
+      <c r="AC44" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -7126,7 +7154,11 @@
       <c r="AB63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC63" s="4" t="inlineStr"/>
+      <c r="AC63" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">

--- a/docs/d/46/inyear.xlsx
+++ b/docs/d/46/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 84 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 78 clubs short</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1221,8 +1221,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1633,8 +1633,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2220,8 +2220,8 @@
       <c r="P15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" s="9" t="n">
-        <v>1</v>
+      <c r="Q15" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R15" s="9" t="n">
         <v>0</v>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>0</v>
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7349,8 +7349,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7652,8 +7652,8 @@
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7955,8 +7955,8 @@
       <c r="Y71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z71" s="9" t="n">
-        <v>0</v>
+      <c r="Z71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA71" s="10" t="n">
         <v>1</v>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12250,8 +12250,8 @@
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
@@ -17885,7 +17885,7 @@
         <v>0</v>
       </c>
       <c r="S171" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T171" s="9" t="n">
         <v>0</v>
@@ -18200,7 +18200,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -18299,7 +18299,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -18629,7 +18629,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -18662,7 +18662,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -18695,7 +18695,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -19025,7 +19025,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>

--- a/docs/d/46/inyear.xlsx
+++ b/docs/d/46/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 78 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 35 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -1019,8 +1019,8 @@
       <c r="Y3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA3" s="10" t="n">
         <v>1</v>
@@ -1215,8 +1215,8 @@
       <c r="W5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X5" s="9" t="n">
-        <v>3</v>
+      <c r="X5" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y5" s="9" t="n">
         <v>0</v>
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1532,8 +1532,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1839,8 +1839,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="X12" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12" s="9" t="n">
         <v>0</v>
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>0</v>
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>76</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>4</v>
       </c>
       <c r="W23" s="10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>7</v>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3382,8 +3382,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3483,8 +3483,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3685,8 +3685,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3869,8 +3869,8 @@
       <c r="S31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T31" s="9" t="n">
-        <v>0</v>
+      <c r="T31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U31" s="9" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="X31" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y31" s="9" t="n">
         <v>0</v>
@@ -3986,14 +3986,14 @@
       <c r="W32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X32" s="9" t="n">
-        <v>0</v>
+      <c r="X32" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z32" s="9" t="n">
-        <v>0</v>
+      <c r="Z32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA32" s="9" t="n">
         <v>0</v>
@@ -4192,8 +4192,8 @@
       <c r="Y34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z34" s="9" t="n">
-        <v>0</v>
+      <c r="Z34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA34" s="9" t="n">
         <v>0</v>
@@ -4491,8 +4491,8 @@
       <c r="W37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X37" s="9" t="n">
-        <v>3</v>
+      <c r="X37" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y37" s="9" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4800,8 +4800,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5103,8 +5103,8 @@
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
@@ -5287,7 +5287,7 @@
         <v>0</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" s="9" t="n">
         <v>0</v>
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5414,8 +5414,8 @@
       <c r="Y46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="9" t="n">
-        <v>0</v>
+      <c r="Z46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA46" s="10" t="n">
         <v>1</v>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5721,8 +5721,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5766,13 +5766,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5811,19 +5811,19 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X50" s="9" t="n">
-        <v>3</v>
+      <c r="X50" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -6329,8 +6329,8 @@
       <c r="W55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X55" s="9" t="n">
-        <v>3</v>
+      <c r="X55" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y55" s="9" t="n">
         <v>0</v>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6440,8 +6440,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
@@ -7849,7 +7849,7 @@
         <v>0</v>
       </c>
       <c r="X70" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y70" s="9" t="n">
         <v>0</v>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="X73" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y73" s="9" t="n">
         <v>0</v>
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8363,8 +8363,8 @@
       <c r="Y75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" s="9" t="n">
-        <v>0</v>
+      <c r="Z75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA75" s="10" t="n">
         <v>1</v>
@@ -8495,7 +8495,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8559,14 +8559,14 @@
       <c r="W77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X77" s="9" t="n">
-        <v>2</v>
+      <c r="X77" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="9" t="n">
-        <v>0</v>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8872,8 +8872,8 @@
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -9002,7 +9002,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9067,13 +9067,13 @@
         <v>0</v>
       </c>
       <c r="X82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9265,13 +9265,13 @@
         <v>0</v>
       </c>
       <c r="X84" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -9567,8 +9567,8 @@
       <c r="W87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X87" s="9" t="n">
-        <v>3</v>
+      <c r="X87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
@@ -10295,7 +10295,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10360,13 +10360,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -10396,7 +10396,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10466,8 +10466,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10990,7 +10990,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11060,8 +11060,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11089,7 +11089,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11159,8 +11159,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -11549,8 +11549,8 @@
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X107" s="9" t="n">
-        <v>3</v>
+      <c r="X107" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11654,8 +11654,8 @@
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="9" t="n">
-        <v>0</v>
+      <c r="Z108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
@@ -11782,7 +11782,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11852,8 +11852,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -11946,7 +11946,7 @@
         <v>0</v>
       </c>
       <c r="X111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12052,8 +12052,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12392,10 +12392,10 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K116" s="4" t="n">
         <v>0</v>
@@ -12448,8 +12448,8 @@
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -12477,7 +12477,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12527,10 +12527,10 @@
         <v>0</v>
       </c>
       <c r="S117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U117" s="9" t="n">
         <v>0</v>
@@ -12873,7 +12873,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12943,8 +12943,8 @@
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="9" t="n">
-        <v>0</v>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -13736,7 +13736,7 @@
         <v>0</v>
       </c>
       <c r="X129" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -13770,7 +13770,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13834,14 +13834,14 @@
       <c r="W130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X130" s="9" t="n">
-        <v>3</v>
+      <c r="X130" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="9" t="n">
-        <v>0</v>
+      <c r="Z130" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA130" s="10" t="n">
         <v>1</v>
@@ -14166,7 +14166,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14236,8 +14236,8 @@
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA134" s="10" t="n">
         <v>1</v>
@@ -14364,7 +14364,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14428,14 +14428,14 @@
       <c r="W136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X136" s="9" t="n">
-        <v>3</v>
+      <c r="X136" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -14463,7 +14463,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14533,8 +14533,8 @@
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="9" t="n">
-        <v>0</v>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
@@ -15128,7 +15128,7 @@
         <v>0</v>
       </c>
       <c r="X143" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
@@ -15360,7 +15360,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15430,8 +15430,8 @@
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="9" t="n">
-        <v>0</v>
+      <c r="Z146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA146" s="10" t="n">
         <v>1</v>
@@ -15523,8 +15523,8 @@
       <c r="W147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X147" s="9" t="n">
-        <v>3</v>
+      <c r="X147" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y147" s="9" t="n">
         <v>0</v>
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -16123,8 +16123,8 @@
       <c r="Y153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z153" s="9" t="n">
-        <v>0</v>
+      <c r="Z153" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA153" s="10" t="n">
         <v>1</v>
@@ -16350,7 +16350,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16420,8 +16420,8 @@
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="9" t="n">
-        <v>0</v>
+      <c r="Z156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA156" s="10" t="n">
         <v>1</v>
@@ -16647,7 +16647,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16712,13 +16712,13 @@
         <v>0</v>
       </c>
       <c r="X159" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z159" s="9" t="n">
-        <v>0</v>
+      <c r="Z159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA159" s="10" t="n">
         <v>1</v>
@@ -16746,7 +16746,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16811,13 +16811,13 @@
         <v>0</v>
       </c>
       <c r="X160" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z160" s="9" t="n">
-        <v>0</v>
+      <c r="Z160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA160" s="10" t="n">
         <v>1</v>
@@ -16944,7 +16944,7 @@
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -17014,8 +17014,8 @@
       <c r="Y162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z162" s="9" t="n">
-        <v>0</v>
+      <c r="Z162" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA162" s="10" t="n">
         <v>1</v>
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -17113,8 +17113,8 @@
       <c r="Y163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z163" s="9" t="n">
-        <v>0</v>
+      <c r="Z163" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA163" s="10" t="n">
         <v>1</v>
@@ -17306,7 +17306,7 @@
         <v>0</v>
       </c>
       <c r="X165" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y165" s="9" t="n">
         <v>0</v>
@@ -17439,7 +17439,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17509,8 +17509,8 @@
       <c r="Y167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z167" s="9" t="n">
-        <v>0</v>
+      <c r="Z167" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA167" s="10" t="n">
         <v>1</v>
@@ -17538,7 +17538,7 @@
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -17602,14 +17602,14 @@
       <c r="W168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X168" s="9" t="n">
-        <v>3</v>
+      <c r="X168" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z168" s="9" t="n">
-        <v>0</v>
+      <c r="Z168" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA168" s="10" t="n">
         <v>1</v>
@@ -17736,7 +17736,7 @@
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>10</v>
@@ -17801,13 +17801,13 @@
         <v>0</v>
       </c>
       <c r="X170" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z170" s="9" t="n">
-        <v>0</v>
+      <c r="Z170" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA170" s="10" t="n">
         <v>1</v>
@@ -18200,7 +18200,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -18266,7 +18266,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -18365,7 +18365,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -18398,7 +18398,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -18464,7 +18464,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -18497,7 +18497,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -18530,7 +18530,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -18596,7 +18596,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -18728,7 +18728,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -18761,7 +18761,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -18794,7 +18794,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -18860,7 +18860,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -18926,7 +18926,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -18959,7 +18959,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -18992,7 +18992,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -19025,7 +19025,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -19058,7 +19058,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -19124,7 +19124,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -19157,7 +19157,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -19190,7 +19190,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -19256,7 +19256,7 @@
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -19289,7 +19289,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -19322,7 +19322,7 @@
         <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -19355,7 +19355,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -19388,7 +19388,7 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -19421,7 +19421,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>

--- a/docs/d/46/inyear.xlsx
+++ b/docs/d/46/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/46/inyear.xlsx
+++ b/docs/d/46/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/46/inyear.xlsx
+++ b/docs/d/46/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/46/inyear.xlsx
+++ b/docs/d/46/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/46/inyear.xlsx
+++ b/docs/d/46/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 35 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 35 clubs short</t>
         </is>
       </c>
     </row>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1307,8 +1307,8 @@
       <c r="T6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U6" s="9" t="n">
-        <v>0</v>
+      <c r="U6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>2</v>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>0</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="9" t="n">
         <v>0</v>
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -1985,13 +1985,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -2502,13 +2502,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2759,8 +2759,8 @@
       <c r="V20" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W20" s="9" t="n">
-        <v>2</v>
+      <c r="W20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X20" s="10" t="n">
         <v>7</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>76</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-27</v>
+        <v>-25</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3060,14 +3060,14 @@
       <c r="T23" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U23" s="9" t="n">
-        <v>0</v>
+      <c r="U23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V23" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W23" s="10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>7</v>
@@ -3124,13 +3124,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3528,17 +3528,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M28" s="8" t="n">
@@ -4237,13 +4237,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4643,13 +4643,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -5358,13 +5358,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X46" s="9" t="n">
         <v>2</v>
@@ -6172,13 +6172,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>4</v>
       </c>
       <c r="W54" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X54" s="10" t="n">
         <v>5</v>
@@ -7087,13 +7087,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>5</v>
@@ -8608,13 +8608,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8953,8 +8953,8 @@
       <c r="S81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T81" s="9" t="n">
-        <v>0</v>
+      <c r="T81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U81" s="9" t="n">
         <v>0</v>
@@ -9002,7 +9002,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9016,13 +9016,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9063,8 +9063,8 @@
       <c r="V82" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W82" s="9" t="n">
-        <v>3</v>
+      <c r="W82" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X82" s="10" t="n">
         <v>5</v>
@@ -9313,13 +9313,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="S87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" s="10" t="n">
         <v>1</v>
@@ -9616,13 +9616,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>4</v>
       </c>
       <c r="W88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>4</v>
@@ -9715,13 +9715,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9814,13 +9814,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9913,13 +9913,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -10210,13 +10210,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10309,13 +10309,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>0</v>
       </c>
       <c r="Q95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" s="9" t="n">
         <v>0</v>
@@ -10608,13 +10608,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>4</v>
       </c>
       <c r="W98" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X98" s="9" t="n">
         <v>0</v>
@@ -10905,13 +10905,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-17</v>
+        <v>-15</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11301,13 +11301,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11400,13 +11400,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11994,13 +11994,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12095,13 +12095,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" s="9" t="n">
         <v>0</v>
@@ -12491,17 +12491,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-17</v>
-      </c>
-      <c r="L117" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12536,7 +12536,7 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12590,13 +12590,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12788,13 +12788,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>4</v>
       </c>
       <c r="W120" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>7</v>
@@ -12887,13 +12887,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-19</v>
+        <v>-17</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>1</v>
       </c>
       <c r="Q121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
@@ -13572,7 +13572,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13627,8 +13627,8 @@
       <c r="T128" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U128" s="9" t="n">
-        <v>0</v>
+      <c r="U128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V128" s="9" t="n">
         <v>0</v>
@@ -14978,13 +14978,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15077,13 +15077,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-16</v>
+        <v>-13</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
@@ -15770,13 +15770,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -16265,13 +16265,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
@@ -16958,13 +16958,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>0</v>
       </c>
       <c r="V162" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W162" s="9" t="n">
         <v>0</v>
@@ -17057,13 +17057,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17453,13 +17453,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
@@ -17479,8 +17479,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P167" s="9" t="n">
-        <v>3</v>
+      <c r="P167" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q167" s="9" t="n">
         <v>0</v>
@@ -18033,7 +18033,7 @@
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>10</v>
@@ -18085,8 +18085,8 @@
       <c r="S173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T173" s="9" t="n">
-        <v>0</v>
+      <c r="T173" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U173" s="9" t="n">
         <v>0</v>
@@ -18332,7 +18332,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -18431,13 +18431,13 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -18464,7 +18464,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -18512,7 +18512,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -18860,7 +18860,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -19139,7 +19139,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -19190,7 +19190,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -19487,7 +19487,7 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -19520,7 +19520,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>

--- a/docs/d/46/inyear.xlsx
+++ b/docs/d/46/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 35 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 35 clubs short</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -1001,8 +1001,8 @@
       <c r="S3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="9" t="n">
-        <v>0</v>
+      <c r="T3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U3" s="9" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>PMI Westchester Toastmasters</t>
+          <t>Project Westchester Toastmasters</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2020,14 +2020,14 @@
       <c r="R13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="9" t="n">
-        <v>1</v>
+      <c r="S13" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T13" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U13" s="9" t="n">
-        <v>0</v>
+      <c r="U13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V13" s="9" t="n">
         <v>1</v>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2235,8 +2235,8 @@
       <c r="U15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="9" t="n">
-        <v>2</v>
+      <c r="V15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2502,13 +2502,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>4</v>
       </c>
       <c r="W20" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X20" s="10" t="n">
         <v>7</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>76</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-25</v>
+        <v>-18</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -3046,13 +3046,13 @@
         </is>
       </c>
       <c r="P23" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q23" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R23" s="9" t="n">
-        <v>0</v>
+      <c r="R23" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S23" s="10" t="n">
         <v>2</v>
@@ -3067,7 +3067,7 @@
         <v>4</v>
       </c>
       <c r="W23" s="10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>7</v>
@@ -4035,13 +4035,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-14</v>
+        <v>-9</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4237,13 +4237,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-22</v>
+        <v>-8</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4845,13 +4845,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-13</v>
+        <v>-9</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5152,13 +5152,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>95</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-26</v>
+        <v>-21</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5188,19 +5188,19 @@
         <v>0</v>
       </c>
       <c r="S44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T44" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V44" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W44" s="9" t="n">
-        <v>1</v>
+      <c r="W44" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X44" s="10" t="n">
         <v>6</v>
@@ -6172,13 +6172,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>4</v>
       </c>
       <c r="W54" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X54" s="10" t="n">
         <v>5</v>
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6321,11 +6321,11 @@
       <c r="U55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="9" t="n">
-        <v>0</v>
+      <c r="V55" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X55" s="10" t="n">
         <v>5</v>
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6626,8 +6626,8 @@
       <c r="S58" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T58" s="9" t="n">
-        <v>0</v>
+      <c r="T58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U58" s="9" t="n">
         <v>0</v>
@@ -6986,13 +6986,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -7296,10 +7296,10 @@
         <v>10</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7796,17 +7796,17 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-24</v>
-      </c>
-      <c r="L70" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M70" s="8" t="n">
@@ -7841,7 +7841,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8200,13 +8200,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8229,8 +8229,8 @@
       <c r="P74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" s="9" t="n">
-        <v>1</v>
+      <c r="Q74" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
@@ -8245,7 +8245,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>0</v>
       </c>
       <c r="Q81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" s="9" t="n">
         <v>0</v>
@@ -9019,10 +9019,10 @@
         <v>19</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9118,10 +9118,10 @@
         <v>10</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9313,13 +9313,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X85" s="10" t="n">
         <v>5</v>
@@ -9412,13 +9412,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9511,17 +9511,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L87" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9913,13 +9913,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>4</v>
       </c>
       <c r="W91" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X91" s="10" t="n">
         <v>4</v>
@@ -10438,7 +10438,7 @@
         <v>1</v>
       </c>
       <c r="Q96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
@@ -10608,13 +10608,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         </is>
       </c>
       <c r="P98" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q98" s="10" t="n">
         <v>2</v>
@@ -10656,7 +10656,7 @@
         <v>4</v>
       </c>
       <c r="W98" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X98" s="9" t="n">
         <v>0</v>
@@ -11287,7 +11287,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11301,13 +11301,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11348,8 +11348,8 @@
       <c r="V105" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W105" s="9" t="n">
-        <v>2</v>
+      <c r="W105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>6</v>
@@ -11386,7 +11386,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11429,8 +11429,8 @@
       <c r="P106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" s="9" t="n">
-        <v>1</v>
+      <c r="Q106" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
@@ -11628,7 +11628,7 @@
         <v>0</v>
       </c>
       <c r="Q108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
@@ -12491,13 +12491,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12887,13 +12887,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-17</v>
+        <v>-15</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>0</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
@@ -13088,10 +13088,10 @@
         <v>19</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13481,13 +13481,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13586,13 +13586,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -14067,7 +14067,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14108,22 +14108,22 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q133" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="Q133" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T133" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U133" s="9" t="n">
-        <v>0</v>
+      <c r="U133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V133" s="10" t="n">
         <v>4</v>
@@ -14678,10 +14678,10 @@
         <v>24</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>0</v>
       </c>
       <c r="Q147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R147" s="9" t="n">
         <v>0</v>
@@ -15674,10 +15674,10 @@
         <v>25</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
@@ -16070,10 +16070,10 @@
         <v>11</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -16268,10 +16268,10 @@
         <v>23</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
@@ -16463,13 +16463,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>0</v>
       </c>
       <c r="V157" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
@@ -16862,10 +16862,10 @@
         <v>33</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
@@ -17453,13 +17453,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>4</v>
       </c>
       <c r="W167" s="10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="X167" s="10" t="n">
         <v>4</v>
@@ -17579,7 +17579,7 @@
         </is>
       </c>
       <c r="P168" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q168" s="9" t="n">
         <v>0</v>
@@ -17876,7 +17876,7 @@
         </is>
       </c>
       <c r="P171" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q171" s="9" t="n">
         <v>0</v>
@@ -18299,7 +18299,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -18365,7 +18365,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -18398,7 +18398,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -18464,7 +18464,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -18596,13 +18596,13 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -18662,7 +18662,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -18695,7 +18695,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -18776,7 +18776,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -18794,7 +18794,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -18908,7 +18908,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -19025,7 +19025,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19058,13 +19058,13 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -19256,13 +19256,13 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
